--- a/03测试用例.xlsx
+++ b/03测试用例.xlsx
@@ -1,105 +1,2010 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr showInkAnnotation="0" defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Study\Junior\fall\mini-semester\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{94E88532-4488-4C41-A3ED-810A5F15776F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr defaultThemeVersion="202300"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{D240F594-8E51-4ACA-AEE5-037EC2373825}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38640" windowHeight="21120"/>
   </bookViews>
   <sheets>
-    <sheet name="测试用例" sheetId="1" r:id="rId1"/>
+    <sheet name="01 用户信息维护" sheetId="1" r:id="rId1"/>
+    <sheet name="02 附近电站与导航" sheetId="2" r:id="rId2"/>
+    <sheet name="03 充电全流程" sheetId="3" r:id="rId3"/>
+    <sheet name="04 管理员登录与销售业绩" sheetId="4" r:id="rId4"/>
+    <sheet name="05 充电站管理" sheetId="5" r:id="rId5"/>
+    <sheet name="06 充电桩管理与状态" sheetId="6" r:id="rId6"/>
+    <sheet name="07 用户管理" sheetId="7" r:id="rId7"/>
+    <sheet name="08 负荷预测与大屏" sheetId="8" r:id="rId8"/>
+    <sheet name="09 通信并发与错误处理" sheetId="9" r:id="rId9"/>
+    <sheet name="10 缺陷清单" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
-  <si>
-    <t>项目名称</t>
-  </si>
-  <si>
-    <t>程序版本</t>
-  </si>
-  <si>
-    <t>功能模块名</t>
-  </si>
-  <si>
-    <t>编制人</t>
-  </si>
-  <si>
-    <t>编制时间</t>
-  </si>
-  <si>
-    <t>功能特性</t>
-  </si>
-  <si>
-    <t>测试目的</t>
-  </si>
-  <si>
-    <t>预置条件</t>
-  </si>
-  <si>
-    <t>用例编号</t>
-  </si>
-  <si>
-    <t>用例说明</t>
-  </si>
-  <si>
-    <t>输入数据</t>
-  </si>
-  <si>
-    <t>预期结果</t>
-  </si>
-  <si>
-    <t>测试结果</t>
-  </si>
-  <si>
-    <t>缺陷编号</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>8</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="636">
+  <si>
+    <t xml:space="preserve">项目名称</t>
+  </si>
+  <si>
+    <t xml:space="preserve">东软电动汽车充电桩应用管理平台</t>
+  </si>
+  <si>
+    <t xml:space="preserve">程序版本</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1.0（协议 docs/protocol.md v1.1）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">功能模块名</t>
+  </si>
+  <si>
+    <t xml:space="preserve">充电用户端 · 用户信息维护</t>
+  </si>
+  <si>
+    <t xml:space="preserve">编制人</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L4（测试与回归）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">编制时间</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">功能特性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.4 基于手机号实现免密登录与用户信息管理：11 位手机号存在即登录，不存在自动注册（昵称「用户」+ 后 4 位、默认灰色头像）；登录后可改昵称、换头像、充值。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">测试目的</t>
+  </si>
+  <si>
+    <t xml:space="preserve">验证免密登录与自动注册规则正确；验证昵称/头像/充值三项信息维护功能；重点覆盖手机号格式、冻结账号、充值金额边界等异常路径。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">预置条件</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 已按 docs/RUNBOOK.md 第 1 节完成构建（bash scripts/build-all.sh）；② 数据库由 docs/db-schema.sql 建库，含 6 电站 / 26 电桩 / 4 种子用户；③ 服务端 ecp-server 已启动并监听配置端口；④ 种子用户 13800138001（正常，余额 20000 分）、13800138006（已冻结）；⑤ t_sys_config.recharge_max = 100000 分</t>
+  </si>
+  <si>
+    <t xml:space="preserve">用例编号</t>
+  </si>
+  <si>
+    <t xml:space="preserve">用例说明</t>
+  </si>
+  <si>
+    <t xml:space="preserve">输入数据</t>
+  </si>
+  <si>
+    <t xml:space="preserve">预期结果</t>
+  </si>
+  <si>
+    <t xml:space="preserve">测试结果</t>
+  </si>
+  <si>
+    <t xml:space="preserve">缺陷编号</t>
+  </si>
+  <si>
+    <t xml:space="preserve">备注</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S1-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">未注册手机号首次登录，验证自动注册规则</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phone=13900001111（库中不存在）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=0；自动创建用户；nickname=「用户1111」（「用户」+手机号后 4 位）；balance=0；avatar 为空串（客户端渲染默认灰色头像）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=0 msg=ok nickname=用户1111 balance=0 avatar=''</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.4 明文规则</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S1-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">已注册手机号免密登录，不需要密码</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phone=13800138001（种子用户）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=0；返回 token；userId=1；balance=20000 分；不校验任何密码</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=0 msg=ok userId=1 balance=20000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.4 免密登录</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S1-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">手机号位数不足</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phone=1380013800（10 位）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=2001；msg=「请输入 11 位手机号」；不创建用户</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=2001 msg=请输入 11 位手机号</t>
+  </si>
+  <si>
+    <t xml:space="preserve">异常路径</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S1-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">手机号含非数字字符</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phone=1380013800a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=2001；msg=「请输入 11 位手机号」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S1-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">手机号为空串</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phone=""</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=2001 或 1001；不得进入自动注册分支</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S1-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">已冻结账号登录被拒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phone=13800138006（t_user.status=1）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=2003；msg=「该账号已被冻结，请联系客服」；不下发 token</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=2003 msg=该账号已被冻结，请联系客服</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.4 冻结风控；与 07 表 S7-07 呼应</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S1-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">修改昵称后回读校验</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1003 nickname=「测试昵称」，随后调 1002 回读</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1003 返回 code=0；1002 返回的 nickname 与提交值一致</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：1003 code=0 msg=ok；1002 回读 nickname=测试昵称</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S1-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">昵称提交空串</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1003 nickname=""</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=1001；msg=「参数错误，请检查输入」；原昵称不被覆盖</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=1001 msg=参数错误，请检查输入</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S1-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">钱包充值（模拟支付）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1005 amount=10000（分，即 100 元）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=0；返回充值后 balance=10000 分；余额实时更新</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=0 msg=ok balance=10000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.4 模拟支付；金额单位为整数分</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S1-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">充值金额超过单笔上限</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1005 amount=100001（上限 recharge_max=100000）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=2005；msg=「金额不合法」；余额不变</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=2005 msg=金额不合法</t>
+  </si>
+  <si>
+    <t xml:space="preserve">边界值 +1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S1-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">充值负数金额</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1005 amount=-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S1-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">未登录状态调用需鉴权接口</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1002，token 为空串</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=1002；msg=「尚未登录，请先登录」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=1002 msg=尚未登录，请先登录</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鉴权边界</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S1-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">从本地选择图片上传作为头像</t>
+  </si>
+  <si>
+    <t xml:space="preserve">个人中心 → 点击头像 → 选择本地 PNG/JPG 文件 → 保存</t>
+  </si>
+  <si>
+    <t xml:space="preserve">文件选择对话框正常弹出；上传后头像区域立即显示所选图片；重新登录后头像仍为该图片（库中存文件路径，非图片二进制）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">待人工执行（GUI 层，脚本无法覆盖）；[说明书] 1.6 图片存文件路径</t>
+  </si>
+  <si>
+    <t xml:space="preserve">充电用户端 · 附近充电站查询与一键导航</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.4 展示当前位置周边充电站，按距离由近及远；卡片显示站名、价格（元/度）、电桩总数/空闲数、距离（公里）；点击可看站内电桩明细；点击距离调用腾讯地图导航，支持驾车/步行两种出行方式。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">验证附近电站列表的排序、字段完整性与模糊搜索；验证站内电桩详情；验证导航页在 QtWebEngine 可用与缺失两种环境下的表现。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 已按 docs/RUNBOOK.md 第 1 节完成构建（bash scripts/build-all.sh）；② 数据库由 docs/db-schema.sql 建库，含 6 电站 / 26 电桩 / 4 种子用户；③ 服务端 ecp-server 已启动并监听配置端口；④ 用户已登录；⑤ 导航用例需 QtWebEngineProcess 可用且 config/app.ini 已配 map/key</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">查询附近电站，校验按距离升序</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1101 lng=114.05, lat=22.55, keyword="", sortBy=0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=0；返回 6 个电站；distance 字段严格非递减</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=0 msg=ok 返回 6 站 distance=[1288, 1576, 9006, 10801, 17159, 23231]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.4 按距离由近及远</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">校验电站卡片字段齐全</t>
+  </si>
+  <si>
+    <t xml:space="preserve">取 S2-01 返回的首个电站对象</t>
+  </si>
+  <si>
+    <t xml:space="preserve">同时包含 stationId / name / address / price / pileTotal / pileIdle / distance；price 单位为分/度，distance 单位为米</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：首站 福田CBD充电站 price=152分/度 空闲3/4 distance=1288m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.4 卡片四要素</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">按关键词模糊搜索电站</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1101 keyword="福田"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=0；返回站名或地址含「福田」的电站</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=0 msg=ok 命中 2 站：['福田CBD充电站', '深圳市民中心充电站']</t>
+  </si>
+  <si>
+    <t xml:space="preserve">站3「深圳市民中心充电站」地址为「深圳市福田区福中三路 1 号」，按地址命中</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">关键词无任何匹配</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1101 keyword="不存在的站名"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=0 且 list 为空数组——查无结果是正常状态，不是错误</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=0 msg=ok list 长度=0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">异常路径；不应返回错误码</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">经纬度越界</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1101 lng=200（合法区间 -180~180）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=1001；msg=「参数错误，请检查输入」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">边界值</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">查看站内电桩详情</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1102 stationId=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=0；返回该站 4 根电桩；每根含 pileId / code / type / status / power 五字段</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=0 msg=ok 共 4 桩，首桩 {'code': 'SZ001-01', 'pileId': 1, 'power': 120, 'status': 1, 'type': 0}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.4 电桩编号/类型/状态/功率</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">查询不存在的电站</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1102 stationId=9999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=3001；msg=「充电站不存在」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=3001 msg=充电站不存在</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">距离显示单位换算</t>
+  </si>
+  <si>
+    <t xml:space="preserve">附近电站页观察首站距离标签（协议返回 1288 米）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">界面显示为「1.3 km」而非「1288」；万米以上不保留小数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">待人工执行（GUI 层，脚本无法覆盖）；[说明书] 1.4 距离（公里）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">一键导航并切换出行方式</t>
+  </si>
+  <si>
+    <t xml:space="preserve">点击电站卡片距离 → 导航页 → 分别点击「驾车」「步行」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QWebEngineView 加载腾讯地图并规划路线；起点为当前位置、终点为目标电站；两种方式均可切换且状态提示同步更新</t>
+  </si>
+  <si>
+    <t xml:space="preserve">待人工执行（GUI 层，脚本无法覆盖）；[说明书] 1.4 驾车/步行多种出行方式</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QtWebEngine 缺失时的降级表现</t>
+  </si>
+  <si>
+    <t xml:space="preserve">卸载/重命名 QtWebEngineProcess 后启动用户端并进入导航页</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不崩溃；导航页以占位说明替代；相关按钮置灰不可点；日志出现「未找到 QtWebEngineProcess，导航页退回占位页」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">待人工执行（GUI 层，脚本无法覆盖）；异常路径，对应 user-client/webengine_env.cpp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">充电用户端 · 电动汽车充电</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.4 完整的「预约—充电—计费—结算」流程；进入充电页面前必须查询是否存在「充电中」的未完成订单，有则提示并强制跳转结算页。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">验证充电主流程闭环；重点覆盖未完成订单拦截、电桩状态冲突、订单状态机、余额不足、重复结算等异常路径——这些是本项目最易漏测的部分。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 已按 docs/RUNBOOK.md 第 1 节完成构建（bash scripts/build-all.sh）；② 数据库由 docs/db-schema.sql 建库，含 6 电站 / 26 电桩 / 4 种子用户；③ 服务端 ecp-server 已启动并监听配置端口；④ 电桩模拟器已启动并注册上线：./build/bin/ecp-pile-sim --port &lt;端口&gt; SZ001-01 SZ001-03（未启动时 1203 恒返回 3005，会被误判为缺陷）；⑤ 种子桩状态：SZ001-01 闲置、SZ001-02 在用、SZ003-04 故障</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3-02a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">进入充电页先查未完成订单（无未完成）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1201，当前用户无进行中订单</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=0；hasUnfinished=false；允许进入充电流程</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=0 msg=ok hasUnfinished=False</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.4 进入充电页必调</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3-01a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">预约闲置电桩</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1202 pileId=1（SZ001-01，状态=闲置）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=0；返回 orderId；电桩转为占用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=0 msg=ok orderId=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">主流程 1/4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">存在未完成订单时再次进入充电页</t>
+  </si>
+  <si>
+    <t xml:space="preserve">已预约未结算，再调 1201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=0；hasUnfinished=true 并带回该订单；客户端据此弹窗提示并强制跳转结算页</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=0 msg=ok hasUnfinished=True orderNo=ORD202609111329038723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.4 强制跳转，本表最关键用例</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">预约已被占用的电桩</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1202 pileId=2（SZ001-02，状态=在用）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=3003；msg=「该充电桩正在使用中」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=3003 msg=该充电桩正在使用中</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">预约故障电桩</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1202 pileId=12（SZ003-04，状态=故障）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=3004；msg=「该充电桩故障，请选择其他电桩」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=3004 msg=该充电桩故障，请选择其他电桩</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.4 故障状态</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">预约不存在的电桩</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1202 pileId=9999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=3002；msg=「充电桩不存在」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=3002 msg=充电桩不存在</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">跳过「开始充电」直接结束</t>
+  </si>
+  <si>
+    <t xml:space="preserve">订单处于已预约状态，直接调 1204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=4003；msg=「当前订单状态不允许该操作」；订单状态不变</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=4003 msg=当前订单状态不允许该操作</t>
+  </si>
+  <si>
+    <t xml:space="preserve">订单状态机拦截</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">对不存在的订单发起结算</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1205 orderId=99999999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=4001；msg=「订单不存在」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=4001 msg=订单不存在</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3-01b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">开始充电</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1203 orderId=&lt;S3-01a 返回值&gt;，电桩已在线</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=0；返回 startTime；服务端经 9005 通知电桩开始累计</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=0 msg=ok startTime=2026-09-11 13:29:03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">主流程 2/4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">电桩离线时开始充电</t>
+  </si>
+  <si>
+    <t xml:space="preserve">停止 ecp-pile-sim 后对新预约订单调 1203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=3005；msg=「充电桩离线，指令无法下发」；订单停留在已预约状态</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=3005 msg=充电桩离线，指令无法下发 （同一离线判定路径，见 06 表 S6-08）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">异常路径；本条与 S6-08 共用离线判定，执行时需手动停模拟器复现</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">充电过程中的实时数据推送</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1203 后保持连接，观察服务端主动下发的 1208 帧</t>
+  </si>
+  <si>
+    <t xml:space="preserve">收到 1208 推送；data 含 orderId / kwh / amount / duration 且随时间递增</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：收到 1 条推送，样例={'amount': 25, 'duration': 3, 'kwh': 0.17, 'orderId': 1}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">服务端主动推送通道</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3-01c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">结束充电并计费</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1204 orderId=&lt;同上&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=0；返回 endTime / kwh / amount；amount = price(分/度) × kwhX100 / 100 向下取整</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=0 msg=ok kwh=0.17 amount=25分</t>
+  </si>
+  <si>
+    <t xml:space="preserve">主流程 3/4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">计费金额必须是整数分</t>
+  </si>
+  <si>
+    <t xml:space="preserve">检查 1204 返回的 amount 字段类型与取值</t>
+  </si>
+  <si>
+    <t xml:space="preserve">amount 为整数（分），不出现浮点数；价格 152 分/度</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：amount=25 类型=int；price=152分/度 kwh=0.17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAUDE.md 硬性规则 3：禁止 double/float 金额</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3-01d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">订单结算并扣减钱包余额</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1205 orderId=&lt;同上&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=0；返回 amount 与扣减后 balance；余额减少额等于账单额</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=0 msg=ok amount=25分 balance=19975分</t>
+  </si>
+  <si>
+    <t xml:space="preserve">主流程 4/4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">结算后生成钱包流水</t>
+  </si>
+  <si>
+    <t xml:space="preserve">结算完成后调 1006 查询流水首条</t>
+  </si>
+  <si>
+    <t xml:space="preserve">新增一条 type=1（支出）记录；amount 与账单一致；remark=「充电扣费」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=0 msg=ok 首条 type=1 amount=25 remark=充电扣费</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">重复结算同一订单</t>
+  </si>
+  <si>
+    <t xml:space="preserve">对已结算订单再次调 1205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=4004；msg=「订单已结算，请勿重复操作」；不重复扣款</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=4004 msg=订单已结算，请勿重复操作</t>
+  </si>
+  <si>
+    <t xml:space="preserve">异常路径；防重复提交</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3-02b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">结算后未完成订单标志复位</t>
+  </si>
+  <si>
+    <t xml:space="preserve">结算完成后再调 1201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=0；hasUnfinished=false；可正常开始下一单</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">余额不足时结算被拒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">用 13800138004（余额 150 分）充电至账单超过余额后调 1205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=2004；msg=「钱包余额不足，请先充值」；不产生负余额</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：账户余额=150分 本单应付=152分 → 1205 code=2004 msg=钱包余额不足，请先充值</t>
+  </si>
+  <si>
+    <t xml:space="preserve">异常路径
+充电 30s 使账单超过余额；时长不足会因应付小于余额而误判为通过</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">取消预约后电桩恢复闲置</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1202 预约 pileId=3 后立即 1206 取消，再查 1102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1206 返回 code=0；该桩 status 回到 1（闲置），可被再次预约</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：1206 code=0 msg=ok；SZ001-03 status=1（1=闲置）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">取消已进入后续状态的订单</t>
+  </si>
+  <si>
+    <t xml:space="preserve">对已开始充电/待结算的订单调 1206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=4003 或 4004；不允许取消</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">未完成订单的界面拦截表现</t>
+  </si>
+  <si>
+    <t xml:space="preserve">持有未结算订单时，在用户端点击底部「充电」进入充电页</t>
+  </si>
+  <si>
+    <t xml:space="preserve">弹出提示「您有未完成的充电订单，请先结算」；点击确定后界面强制跳转到结算页，且无法绕过返回充电页</t>
+  </si>
+  <si>
+    <t xml:space="preserve">待人工执行（GUI 层，脚本无法覆盖）；[说明书] 1.4 明文要求，答辩必演示</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PC 管理端 · 管理员登录与销售业绩</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.4 管理员账号密码存于数据库管理员表（默认 admin/123456），登录后进入管理后台；销售业绩以 QChart 展示近 7 日 / 近 30 日营收趋势折线图，并展示今日营收、本月营收、总营收三大核心数字指标。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">验证管理员身份校验与鉴权边界；验证三大营收指标与两种时间维度的趋势数据。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 已按 docs/RUNBOOK.md 第 1 节完成构建（bash scripts/build-all.sh）；② 数据库由 docs/db-schema.sql 建库，含 6 电站 / 26 电桩 / 4 种子用户；③ 服务端 ecp-server 已启动并监听配置端口；④ t_admin 含默认账号 admin/123456；⑤ 营收类用例会被执行过程中产生的订单影响，建议在库副本上执行或只校验结构与点数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S4-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">管理员默认账号登录</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2001 account=admin, password=123456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=0；返回 token 与 adminId；进入管理后台主界面</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=0 msg=ok adminId=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.4 默认初始账号</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S4-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">管理员密码错误</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2001 account=admin, password=wrong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=5001；msg=「账号或密码错误」；不下发 token</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=5001 msg=账号或密码错误</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S4-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">管理员账号不存在</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2001 account=nobody</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=5001；错误文案与密码错误一致，不泄露账号是否存在</t>
+  </si>
+  <si>
+    <t xml:space="preserve">异常路径；[说明书] 2.2 数据安全</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S4-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">账号密码均为空</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2001 account="", password=""</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=1001 或 5001；不下发 token</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S4-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">未登录查询营收数据</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2301，token 为空</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S4-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">今日 / 本月 / 总营收三指标</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2301（管理员已登录）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=0；返回 today / month / total 三个字段，单位为分</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=0 msg=ok today=25 month=25 total=25（单位：分）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.4 三大核心数字指标</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S4-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">近 7 日营收趋势（含补零）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2302 days=7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=0；返回恰好 7 个数据点；无订单的日期补 amount=0 而非缺失</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=0 msg=ok 返回 7 个点，首={'amount': 0, 'date': '2026-09-05'} 末={'amount': 25, 'date': '2026-09-11'}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.4；补零保证折线连续</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S4-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">近 30 日营收趋势</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2302 days=30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=0；返回恰好 30 个数据点</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=0 msg=ok 返回 30 个点</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S4-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">趋势图时间维度切换</t>
+  </si>
+  <si>
+    <t xml:space="preserve">数据总览页点击「近7日」与「近30日」按钮</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QChart 折线图重绘；图表标题同步改为「近 7 日营收趋势」/「近 30 日营收趋势」；X 轴刻度数量随之变化；金额按元显示（整数分 ÷ 100）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">待人工执行（GUI 层，脚本无法覆盖）；[说明书] 1.4 可切换时间维度</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PC 管理端 · 充电站管理</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.4 列表展示充电站 ID、站名、详细地址、经纬度、总电桩数、当前在线率；点击电站行可查看该站所有电桩的实时状态明细；支持填写站名、地址、经纬度、电桩数量等字段完成新增（模拟新增）。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">验证电站列表字段完整性与分页；验证站内详情下钻；验证新增电站的正常与异常入参；并验证管理端接口不被用户身份越权调用。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 已按 docs/RUNBOOK.md 第 1 节完成构建（bash scripts/build-all.sh）；② 数据库由 docs/db-schema.sql 建库，含 6 电站 / 26 电桩 / 4 种子用户；③ 服务端 ecp-server 已启动并监听配置端口；④ 管理员已登录并持有 token；⑤ 种子库含 6 个电站</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S5-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">电站列表字段完整性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2101 page=1, size=10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=0；每行含 stationId / name / address / lng / lat / pileTotal / onlineRate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=0 msg=ok total=6 首行={'address': '深圳市福田区福华三路 88 号', 'lat': 22.541, 'lng': 114.0579, 'name': '福田CBD充电站', 'onlineRate': 100, 'pileTotal': 4, 'stationId': 1}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.4 列表六要素</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S5-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">电站列表分页</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2101 page=1, size=3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=0；本页返回 3 行；total 仍为全量 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=0 msg=ok 本页 3 行 total=6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S5-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">点击电站行查看站内电桩明细</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2103 stationId=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=0；返回该站全部 4 根电桩的实时状态</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=0 msg=ok 桩数=4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.4 站内详情</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S5-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">新增电站（模拟新增）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2102 name=测试新增站, address=深圳市测试路 1 号, lng=114.06, lat=22.54, price=150, pileCount=2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=0；返回新 stationId；列表刷新后可见该站</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=0 msg=ok 新 stationId=7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.4 模拟新增</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S5-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">新增电站缺必填字段</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2102 仅传 name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=1001；msg=「参数错误，请检查输入」；不产生半截数据</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S5-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">新增电站经纬度越界</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2102 lng=999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=1001；不落库</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S5-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">查看不存在电站的详情</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2103 stationId=9999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S5-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">用户身份越权调用管理端接口</t>
+  </si>
+  <si>
+    <t xml:space="preserve">以用户端登录取得的 token 调 2101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=1004；msg=「无操作权限」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=1004 msg=无操作权限</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 2.2 数据安全</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S5-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">新增电站超时后的界面提示</t>
+  </si>
+  <si>
+    <t xml:space="preserve">断开服务端后在新增电站对话框点击确定</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不静默失败；提示「新增电站响应超时，操作结果未知；请先刷新并核对，避免重复新增」；不自动重试造成重复新增</t>
+  </si>
+  <si>
+    <t xml:space="preserve">待人工执行（GUI 层，脚本无法覆盖）；异常路径，对应 admin-client/station_page.cpp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PC 管理端 · 充电桩管理与电桩状态</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.4 列表展示电桩编号、所属电站、类型（快充/慢充）、功率（kW）、当前状态、累计充电次数、累计充电时长；选中电桩后可执行「远程重启」；电桩状态以表格展示在用/闲置/故障三类的数量及占比百分比。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">验证电桩列表七个字段与筛选；验证状态分布统计口径；重点验证远程重启在在线、离线、不存在三种情形下的表现。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 已按 docs/RUNBOOK.md 第 1 节完成构建（bash scripts/build-all.sh）；② 数据库由 docs/db-schema.sql 建库，含 6 电站 / 26 电桩 / 4 种子用户；③ 服务端 ecp-server 已启动并监听配置端口；④ 管理员已登录；⑤ 模拟器已拉起 SZ001-01（在线），SZ001-04 保持未上线以便验证离线分支；⑥ 种子库 26 根电桩（含新增站）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S6-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">电桩列表字段完整性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2111 page=1, size=30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=0；每行含 pileId / code / stationName / type / power / status / chargeCount / chargeDuration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=0 msg=ok total=26 首行={'chargeCount': 2, 'chargeDuration': 34, 'code': 'SZ001-01', 'pileId': 1, 'power': 120, 'stationName': '福田CBD充电站', 'status': 1, 'type': 0}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.4 列表七要素</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S6-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">按所属电站筛选电桩</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2111 stationId=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=0；仅返回站 1 的 4 根电桩</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=0 msg=ok 返回 4 桩（站1 应为 4）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S6-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">电桩类型只有快充/慢充两种</t>
+  </si>
+  <si>
+    <t xml:space="preserve">统计列表中 type 字段的全部取值</t>
+  </si>
+  <si>
+    <t xml:space="preserve">取值集合 ⊆ {0=快充, 1=慢充}；不出现第三种</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：type 取值集合=[0, 1]（0=快充 1=慢充）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.4 类型两种</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S6-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">电桩状态只有三种</t>
+  </si>
+  <si>
+    <t xml:space="preserve">统计列表中 status 字段的全部取值</t>
+  </si>
+  <si>
+    <t xml:space="preserve">取值集合 ⊆ {0=在用, 1=闲置, 2=故障}；不出现第四种</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：status 取值集合=[0, 1, 2]（0=在用 1=闲置 2=故障）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.4 状态三种</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S6-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">电桩状态分布统计</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=0；返回在用/闲置/故障三类数量与总数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=0 msg=ok 在用=8 闲置=14 故障=4 合计=26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.4 状态分布</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S6-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">状态分布数量自洽（占比合计 100%）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">校验 inUse + idle + fault 是否等于 total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">三类之和严格等于总数，否则界面占比合计不为 100%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：26 == total 26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">统计口径一致性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S6-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">远程重启在线电桩</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2112 pileId=1（SZ001-01，模拟器在线）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=0；服务端经 9003 向该桩下发重启指令；模拟器日志出现「SZ001-01 收到远程重启指令，正在重启…」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=0 msg=ok ；模拟器日志已确认收到 9003 重启指令</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.4 远程重启；需两端日志对照</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S6-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">远程重启未上线的电桩</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2112 pileId=4（SZ001-04，未注册）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=3005；msg=「充电桩离线，指令无法下发」；不静默成功</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=3005 msg=充电桩离线，指令无法下发</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S6-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">远程重启不存在的电桩</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2112 pileId=9999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S6-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">累计充电时长的界面格式化</t>
+  </si>
+  <si>
+    <t xml:space="preserve">电桩管理页观察「累计充电时长」列（协议返回秒数）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">显示为「X小时Y分钟」或「Y分钟」，不直接显示原始秒数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">待人工执行（GUI 层，脚本无法覆盖）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S6-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">远程重启的二次确认与结果反馈</t>
+  </si>
+  <si>
+    <t xml:space="preserve">选中电桩 → 点击「远程重启」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">弹出确认框「确定要重启电桩 X 吗？重启期间该桩将短暂不可用。」；取消则不下发；确认后状态栏提示「重启指令已下发」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">待人工执行（GUI 层，脚本无法覆盖）；防误触</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PC 管理端 · 用户管理</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.4 列表展示用户 ID、手机号、昵称、钱包余额、注册时间、状态（正常/冻结）；管理员可手动冻结/解冻用户账号用于风控；支持按手机号模糊搜索用户。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">验证用户列表与手机号模糊搜索；验证冻结/解冻的完整风控闭环——包括冻结后在线会话立即失效、重新登录被拒、解冻后恢复正常。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 已按 docs/RUNBOOK.md 第 1 节完成构建（bash scripts/build-all.sh）；② 数据库由 docs/db-schema.sql 建库，含 6 电站 / 26 电桩 / 4 种子用户；③ 服务端 ecp-server 已启动并监听配置端口；④ 管理员已登录；⑤ 用户 13800138001 已在另一连接上登录并持有有效 token（用于验证冻结时的会话失效）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S7-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">用户列表字段完整性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2201 page=1, size=10, phoneLike=""</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=0；每行含 userId / phone / nickname / balance / createTime / status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=0 msg=ok total=5 首行={'balance': 10000, 'createTime': '2026-09-11 13:29:03', 'nickname': '测试昵称', 'phone': '13900001111', 'status': 0, 'userId': 5}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.4 列表六要素
+phoneLike 为必填参数，查全部需显式传空串</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S7-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">按手机号模糊搜索</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2201 phoneLike="1380013800"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=0；仅返回手机号包含该片段的用户</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=0 msg=ok 命中 4 人：['13800138006', '13800138004', '13800138002', '13800138001']</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.4 手机号模糊搜索</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S7-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">模糊搜索无匹配</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2201 phoneLike="99999"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=0 且 list 为空数组，不返回错误码</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=0 msg=ok 命中 0 人</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S7-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">冻结用户账号</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2202 userId=1, status=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=0；t_user.status 置为 1；列表状态列显示「冻结」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=0 msg=ok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.4 风控冻结</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S7-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">冻结后该用户在线会话立即失效</t>
+  </si>
+  <si>
+    <t xml:space="preserve">用冻结前取得的旧 token 调 1002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=1003；msg=「登录已过期，请重新登录」；客户端应清空本地 token 并跳转登录页，而非静默重试</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：旧 token 调 1002 → code=1003 msg=登录已过期，请重新登录</t>
+  </si>
+  <si>
+    <t xml:space="preserve">docs/protocol.md 第 6 节明文；最易漏测的一条</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S7-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">冻结后重新登录被拒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1001 phone=13800138001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=2003；msg=「该账号已被冻结，请联系客服」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">与 01 表 S1-06 呼应</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S7-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">解冻用户账号</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2202 userId=1, status=0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=0；status 回到 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S7-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">解冻后恢复正常登录</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=0；正常下发 token</t>
+  </si>
+  <si>
+    <t xml:space="preserve">风控闭环收尾</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S7-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">冻结不存在的用户</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2202 userId=99999, status=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=2002；msg=「用户不存在」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=2002 msg=用户不存在</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S7-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">status 传非法值</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2202 userId=1, status=7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=1001；不修改任何用户状态</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S7-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">冻结/解冻按钮与状态列联动</t>
+  </si>
+  <si>
+    <t xml:space="preserve">用户管理页选中一行 → 点击「冻结」→ 观察列表</t>
+  </si>
+  <si>
+    <t xml:space="preserve">操作成功后状态列立即刷新为「冻结」，按钮文案变为「解冻」；无需手动刷新页面</t>
+  </si>
+  <si>
+    <t xml:space="preserve">数据端 · 负荷预测与可视化大屏</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.4 基于时序机器学习预测未来 1h / 6h / 24h 各站点的充电负荷、空闲桩数量、高峰充电时段；用户端据此优先推荐低拥堵、高空闲率的充电站，管理端据此提供负荷预警。大屏轮询只读快照展示全局态势。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">验证 2305 预测查询的三个 horizon 与异常入参；验证无预测数据时的降级语义；验证 1101 低拥堵推荐排序；验证大屏图表渲染与数据口径一致性。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 已按 docs/RUNBOOK.md 第 1 节完成构建（bash scripts/build-all.sh）；② 数据库由 docs/db-schema.sql 建库，含 6 电站 / 26 电桩 / 4 种子用户；③ 服务端 ecp-server 已启动并监听配置端口；④ 管理员已登录；⑤ 预测类用例需先执行 .venv/bin/python ml/predict.py 回写 t_load_forecast，否则只能验证空数据分支；⑥ 大屏用例需先 ml/export_snapshot.py 导出快照并起静态服务</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S8-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">查询全站 1 小时负荷预测</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2305 stationId=0, horizon=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=0；返回各站 horizon=1 的预测记录（loadKw / idlePile / isPeak / congestion）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=0 msg=ok 返回 0 条</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.4 未来 1 小时</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S8-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">查询全站 6 小时负荷预测</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2305 stationId=0, horizon=6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=0；返回 horizon=6 的记录</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.4 未来 6 小时</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S8-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">查询全站 24 小时负荷预测</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2305 stationId=0, horizon=24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=0；返回 horizon=24 的记录</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.4 未来 24 小时</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S8-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">horizon 传协议未定义的值</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2305 horizon=2（仅允许 1/6/24）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S8-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">库中无预测数据时的降级语义</t>
+  </si>
+  <si>
+    <t xml:space="preserve">未执行 predict.py 的库上调 2305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=0 且 list 为空数组——预测缺失是正常状态，不新增错误码</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=0 msg=ok list=[]（本库未跑 predict.py）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">docs/protocol.md 2305 明文</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S8-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">用户端低拥堵推荐排序</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1101 sortBy=1（服务端按 t_load_forecast 预测拥堵度升序）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=0；有预测的站按 congestion 升序排列在前</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=0 msg=ok congestion 序列=[-1, -1, -1, -1, -1, -1, -1]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.4；本库无预测数据，完整验证见备注</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S8-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">无预测数据的站 congestion 填 -1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">检查 1101 返回中未参与预测的站</t>
+  </si>
+  <si>
+    <t xml:space="preserve">congestion=-1 且 idleForecast=-1，不能填 0——0 在拥堵度语义中表示「最不拥堵」，会把无数据的站排到推荐第一位</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：congestion=[-1, -1, -1, -1, -1, -1, -1]，全部为 -1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ml/CLAUDE.md 已落地建模决策</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S8-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">有预测数据时的推荐排序回归</t>
+  </si>
+  <si>
+    <t xml:space="preserve">在含 t_load_forecast 的库上分别调 1101 sortBy=0 与 sortBy=1，比对站序</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sortBy=1 的站序严格按 congestion 升序，且与 sortBy=0（按距离）不同；用户端本地重排后站序与服务端返回一致，不被覆盖</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：charging.db 6 站预测数据下，服务端 sortBy=1 站序 [4,1,3,6,5,2]；修复前用户端本地重排为 [1,3,4,2,6,5]（拥堵度最低的站 4 掉到第 3 位）；修复后本地重排与服务端逐位一致</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUG-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">该缺陷由本用例发现，已修复并回归</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S8-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大屏图表渲染与轮询刷新</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ml/export_snapshot.py 导出后，浏览器打开 dataviz/index.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">七张图表全部渲染出非空数据；倒计时到点后自动重新拉取快照；快照过期时页面给出明确提示而非静默展示旧数据</t>
+  </si>
+  <si>
+    <t xml:space="preserve">待人工执行（GUI 层，脚本无法覆盖）；已由 ml/selftest.py 第 41 项自动覆盖渲染部分</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S8-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大屏与管理端的营收口径一致</t>
+  </si>
+  <si>
+    <t xml:space="preserve">对比 snapshot.json 的 revenue/trend/status 与管理端 2301/2302/2303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">两侧数值逐项一致（含补零行为），不出现「两个形状」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：ml/selftest.py 第 36–38 项断言全部 PASS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">已由 .venv/bin/python ml/selftest.py 自动覆盖</t>
+  </si>
+  <si>
+    <t xml:space="preserve">服务端 · 通信协议、并发与错误处理</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.6 网络通信由 Socket 编程实现，程序主框架为多线程结构；[说明书] 2.2 通信数据结构设计能够安全稳定地实现数据传输、合理考虑数据安全；[说明书] 2.3 需设计完整的错误处理机制。本项目报文为 4 字节大端长度头 + UTF-8 JSON 体。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">验证 TCP 字节流下的粘包/半包处理；验证非法报文与超长长度头的防御；验证鉴权四种边界；验证线程池并发正确性；验证错误码文案与定义一致。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 已按 docs/RUNBOOK.md 第 1 节完成构建（bash scripts/build-all.sh）；② 数据库由 docs/db-schema.sql 建库，含 6 电站 / 26 电桩 / 4 种子用户；③ 服务端 ecp-server 已启动并监听配置端口；④ 服务端 pool_size=4；⑤ 管理员与普通用户各持一个有效 token</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S9-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">粘包：两个完整报文一次性发出</t>
+  </si>
+  <si>
+    <t xml:space="preserve">同一 socket 一次 send 拼接 2301 与 2303 两个完整帧</t>
+  </si>
+  <si>
+    <t xml:space="preserve">服务端按长度头正确切分；两条响应的 seq 分别回填 901 与 902，互不串包</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：分别收到 seq=901(cmd 2301) 与 seq=902(cmd 2303)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAUDE.md 硬性规则 1；TCP 无消息边界</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S9-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">半包：单个报文分两次发出</t>
+  </si>
+  <si>
+    <t xml:space="preserve">先发长度头 + 前 10 字节，停顿 0.4s 后再发剩余部分</t>
+  </si>
+  <si>
+    <t xml:space="preserve">服务端缓存等齐后才处理；返回正确响应，不丢帧不误判</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：等齐后正确响应 seq=903 code=0 msg=ok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAUDE.md 硬性规则 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S9-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">报文体不是合法 JSON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">发送长度头正确但内容为截断 JSON 的帧</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=1006「报文格式错误」，或服务端主动断开连接；进程不崩溃</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=1006 msg=报文格式错误</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S9-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">长度头声明值远超上限</t>
+  </si>
+  <si>
+    <t xml:space="preserve">长度头填 99999999，实际只发 16 字节</t>
+  </si>
+  <si>
+    <t xml:space="preserve">服务端拒绝该帧并断开连接；不按声明值分配内存（防内存耗尽）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：服务端拒绝并断开（RuntimeError）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 2.2 安全稳定
+FrameCodec 上限保护，断连可接受</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S9-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">未知命令字</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cmd=9999（协议表中不存在）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=1005；msg=「不支持的请求类型」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=1005 msg=不支持的请求类型</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 2.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S9-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">需鉴权接口未携带 token</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2303，token=""</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鉴权边界 1/4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S9-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">携带伪造 token</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2303，token=deadbeef…（32 位随机十六进制）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=1003；msg=「登录已过期，请重新登录」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：code=1003 msg=登录已过期，请重新登录</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鉴权边界 2/4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S9-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">用户 token 调用管理端接口</t>
+  </si>
+  <si>
+    <t xml:space="preserve">以用户 token 调 2303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code=1004；msg=「无操作权限」；角色隔离生效</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鉴权边界 3/4；[说明书] 2.2 数据安全</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S9-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seq 原样回填以匹配请求与响应</t>
+  </si>
+  <si>
+    <t xml:space="preserve">发送任意请求并记录 seq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">响应的 seq 与 cmd 均与请求一致，客户端据此配对</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：请求 seq=1 响应 seq=1 cmd=2301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">协议第 3 节</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S9-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">多连接并发请求</t>
+  </si>
+  <si>
+    <t xml:space="preserve">同时建立 8 个连接，各自发送 2303（线程池 pool_size=4）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 个连接全部返回正确且一致的结果；无串包、无数据竞争、无崩溃</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：8/8 个连接返回正确结果</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[说明书] 1.6 多线程主框架；连接数大于线程数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S9-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">错误码文案与定义一致</t>
+  </si>
+  <si>
+    <t xml:space="preserve">抽样触发错误码，比对 msg 与 common/error_code.h 的 errMsg()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">文案逐字一致；[说明书] 2.3 要求说清发生了什么，不得只回「操作失败」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过（2026-09-11）
+实测：抽样 code=2001 msg='请输入 11 位手机号'，与 errMsg() 定义逐字一致</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S9-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">服务端未启动时客户端的表现</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不启动 ecp-server，直接启动 ecp-admin / ecp-user 并尝试登录</t>
+  </si>
+  <si>
+    <t xml:space="preserve">客户端不崩溃、不卡死；给出可读的连接失败提示；重试后可正常连上</t>
+  </si>
+  <si>
+    <t xml:space="preserve">待人工执行（GUI 层，脚本无法覆盖）；异常路径，断网场景</t>
+  </si>
+  <si>
+    <t xml:space="preserve">说明</t>
+  </si>
+  <si>
+    <t xml:space="preserve">缺陷编号与各用例表「缺陷编号」列一一对应。状态取值：待修复 / 修复中 / 已修复并回归 / 不予修复（需写明理由）。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L4（测试与回归）　编制时间 2026-09-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">发现用例</t>
+  </si>
+  <si>
+    <t xml:space="preserve">缺陷标题</t>
+  </si>
+  <si>
+    <t xml:space="preserve">所在文件</t>
+  </si>
+  <si>
+    <t xml:space="preserve">现象与影响</t>
+  </si>
+  <si>
+    <t xml:space="preserve">严重级</t>
+  </si>
+  <si>
+    <t xml:space="preserve">状态</t>
+  </si>
+  <si>
+    <t xml:space="preserve">修复说明</t>
+  </si>
+  <si>
+    <t xml:space="preserve">用户端低拥堵推荐失效</t>
+  </si>
+  <si>
+    <t xml:space="preserve">user-client/main_window.cpp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">客户端向服务端请求 sortBy=1（按预测拥堵度排序）后，又用 pileIdle（当前空闲数）对返回列表做本地重排，把服务端基于 t_load_forecast 排好的顺序整个覆盖掉，导致 [说明书] 1.4「在用户端优先推荐低拥堵、高空闲率的充电站」实际未生效。实测 6 站预测数据下，拥堵度最低的站从第 1 位被挤到第 3 位。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">严重（说明书明文功能未生效）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">已修复并回归</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本地重排改用 congestion 升序，无预测的 -1 排最后，再退回 pileIdle/距离；站点卡片增加预测拥堵度与 1 小时后空闲桩数展示。修复记录见 docs/conventions.md 第 3.1 节 2026-09-11 条目</t>
   </si>
 </sst>
 </file>
@@ -594,236 +2499,3582 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E90D490-AC6D-4F3A-9176-FEA7D2C82080}">
-  <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultColWidth="12.75" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr defaultColWidth="12.75" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="9.625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="23.625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="13.125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="16.375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="17.125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="30" style="3" customWidth="1"/>
+    <col min="3" max="3" width="26" style="3" customWidth="1"/>
+    <col min="4" max="4" width="34" style="2" customWidth="1"/>
+    <col min="5" max="5" width="30" style="3" customWidth="1"/>
     <col min="6" max="6" width="10.625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="6.625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="18" style="3" customWidth="1"/>
     <col min="8" max="16384" width="12.75" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:7" ht="24.95" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
       <c r="C1" s="14"/>
       <c r="D1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>3</v>
+      </c>
       <c r="F1" s="15"/>
       <c r="G1" s="14"/>
     </row>
-    <row r="2" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:7" ht="24.95" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="13"/>
+        <v>4</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>5</v>
+      </c>
       <c r="C2" s="15"/>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="15"/>
       <c r="G2" s="14"/>
     </row>
-    <row r="3" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:7" ht="24.95" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="13"/>
+        <v>6</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>7</v>
+      </c>
       <c r="C3" s="14"/>
       <c r="D3" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="16"/>
+        <v>8</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>9</v>
+      </c>
       <c r="F3" s="17"/>
       <c r="G3" s="18"/>
     </row>
-    <row r="4" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:7" ht="36.00" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="13"/>
+        <v>10</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>11</v>
+      </c>
       <c r="C4" s="15"/>
       <c r="D4" s="15"/>
       <c r="E4" s="15"/>
       <c r="F4" s="15"/>
       <c r="G4" s="14"/>
     </row>
-    <row r="5" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:7" ht="24.95" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="13"/>
+        <v>12</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>13</v>
+      </c>
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
       <c r="E5" s="15"/>
       <c r="F5" s="15"/>
       <c r="G5" s="14"/>
     </row>
-    <row r="6" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:7" ht="36.00" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="13"/>
+        <v>14</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>15</v>
+      </c>
       <c r="C6" s="15"/>
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
       <c r="F6" s="15"/>
       <c r="G6" s="14"/>
     </row>
-    <row r="7" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:7" ht="36" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-    </row>
-    <row r="9" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.15">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="64.00" customHeight="1">
+      <c r="A8" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="36.00" customHeight="1">
       <c r="A9" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
+        <v>29</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>33</v>
+      </c>
       <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-    </row>
-    <row r="10" spans="1:7" ht="50.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G9" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="36.00" customHeight="1">
       <c r="A10" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
+        <v>35</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>39</v>
+      </c>
       <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-    </row>
-    <row r="11" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G10" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="36.00" customHeight="1">
       <c r="A11" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="10"/>
+        <v>41</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>39</v>
+      </c>
       <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-    </row>
-    <row r="12" spans="1:7" ht="50.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G11" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="36.00" customHeight="1">
       <c r="A12" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="10"/>
+        <v>45</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>39</v>
+      </c>
       <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-    </row>
-    <row r="13" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G12" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="50.00" customHeight="1">
       <c r="A13" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
+        <v>49</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>53</v>
+      </c>
       <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-    </row>
-    <row r="14" spans="1:7" ht="50.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G13" s="10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="36.00" customHeight="1">
       <c r="A14" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
+        <v>55</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="F14" s="10"/>
       <c r="G14" s="10"/>
     </row>
-    <row r="15" spans="1:7" ht="50.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:7" ht="36.00" customHeight="1">
       <c r="A15" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
+        <v>60</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>64</v>
+      </c>
       <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A16" s="9"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="10"/>
+      <c r="G15" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="50.00" customHeight="1">
+      <c r="A16" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>69</v>
+      </c>
       <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A17" s="9"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="10"/>
+      <c r="G16" s="10" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A17" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>75</v>
+      </c>
       <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="D18" s="12"/>
+      <c r="G17" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A18" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A19" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="64.00" customHeight="1">
+      <c r="A20" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="E20" s="11"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10" t="s">
+        <v>90</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B6:G6"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="E3:G3"/>
     <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B6:G6"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
-  <headerFooter alignWithMargins="0"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" horizontalDpi="1200" verticalDpi="1200"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultColWidth="12.75" defaultRowHeight="12"/>
+  <cols>
+    <col min="1" max="1" width="11" style="3" customWidth="1"/>
+    <col min="2" max="2" width="10" style="3" customWidth="1"/>
+    <col min="3" max="3" width="22" style="3" customWidth="1"/>
+    <col min="4" max="4" width="26" style="3" customWidth="1"/>
+    <col min="5" max="5" width="46" style="3" customWidth="1"/>
+    <col min="6" max="6" width="14" style="3" customWidth="1"/>
+    <col min="7" max="7" width="12" style="3" customWidth="1"/>
+    <col min="8" max="8" width="42" style="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="14"/>
+    </row>
+    <row r="2" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A2" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>621</v>
+      </c>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="14"/>
+    </row>
+    <row r="3" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>622</v>
+      </c>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="14"/>
+    </row>
+    <row r="4" spans="1:8" ht="36" customHeight="1">
+      <c r="A4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="106.00" customHeight="1">
+      <c r="A5" s="9" t="s">
+        <v>537</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>630</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>631</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>632</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>633</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>635</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr defaultColWidth="12.75" defaultRowHeight="12"/>
+  <cols>
+    <col min="1" max="1" width="9.625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="30" style="3" customWidth="1"/>
+    <col min="3" max="3" width="26" style="3" customWidth="1"/>
+    <col min="4" max="4" width="34" style="2" customWidth="1"/>
+    <col min="5" max="5" width="30" style="3" customWidth="1"/>
+    <col min="6" max="6" width="10.625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="18" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="12.75" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="24.95" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="14"/>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="15"/>
+      <c r="G1" s="14"/>
+    </row>
+    <row r="2" spans="1:7" ht="24.95" customHeight="1">
+      <c r="A2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="1:7" ht="24.95" customHeight="1">
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="14"/>
+      <c r="D3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="17"/>
+      <c r="G3" s="18"/>
+    </row>
+    <row r="4" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="14"/>
+    </row>
+    <row r="5" spans="1:7" ht="24.95" customHeight="1">
+      <c r="A5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="14"/>
+    </row>
+    <row r="6" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="14"/>
+    </row>
+    <row r="7" spans="1:7" ht="36" customHeight="1">
+      <c r="A7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="50.00" customHeight="1">
+      <c r="A8" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="64.00" customHeight="1">
+      <c r="A9" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="78.00" customHeight="1">
+      <c r="A10" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A11" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A12" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="64.00" customHeight="1">
+      <c r="A13" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A14" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="64.00" customHeight="1">
+      <c r="A15" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E15" s="11"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="78.00" customHeight="1">
+      <c r="A16" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="E16" s="11"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="78.00" customHeight="1">
+      <c r="A17" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="E17" s="11"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10" t="s">
+        <v>149</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B6:G6"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" horizontalDpi="1200" verticalDpi="1200"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G28"/>
+  <sheetFormatPr defaultColWidth="12.75" defaultRowHeight="12"/>
+  <cols>
+    <col min="1" max="1" width="9.625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="30" style="3" customWidth="1"/>
+    <col min="3" max="3" width="26" style="3" customWidth="1"/>
+    <col min="4" max="4" width="34" style="2" customWidth="1"/>
+    <col min="5" max="5" width="30" style="3" customWidth="1"/>
+    <col min="6" max="6" width="10.625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="18" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="12.75" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="24.95" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="14"/>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="15"/>
+      <c r="G1" s="14"/>
+    </row>
+    <row r="2" spans="1:7" ht="24.95" customHeight="1">
+      <c r="A2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="1:7" ht="24.95" customHeight="1">
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="14"/>
+      <c r="D3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="17"/>
+      <c r="G3" s="18"/>
+    </row>
+    <row r="4" spans="1:7" ht="24.95" customHeight="1">
+      <c r="A4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="14"/>
+    </row>
+    <row r="5" spans="1:7" ht="24.95" customHeight="1">
+      <c r="A5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="14"/>
+    </row>
+    <row r="6" spans="1:7" ht="50.00" customHeight="1">
+      <c r="A6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="14"/>
+    </row>
+    <row r="7" spans="1:7" ht="36" customHeight="1">
+      <c r="A7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A8" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A9" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="50.00" customHeight="1">
+      <c r="A10" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A11" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A12" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A13" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A14" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A15" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A16" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="64.00" customHeight="1">
+      <c r="A17" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="50.00" customHeight="1">
+      <c r="A18" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="50.00" customHeight="1">
+      <c r="A19" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="50.00" customHeight="1">
+      <c r="A20" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A21" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="50.00" customHeight="1">
+      <c r="A22" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+    </row>
+    <row r="23" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A23" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A24" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+    </row>
+    <row r="25" spans="1:7" ht="64.00" customHeight="1">
+      <c r="A25" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A26" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+    </row>
+    <row r="27" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A27" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="78.00" customHeight="1">
+      <c r="A28" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="E28" s="11"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10" t="s">
+        <v>269</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B6:G6"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" horizontalDpi="1200" verticalDpi="1200"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultColWidth="12.75" defaultRowHeight="12"/>
+  <cols>
+    <col min="1" max="1" width="9.625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="30" style="3" customWidth="1"/>
+    <col min="3" max="3" width="26" style="3" customWidth="1"/>
+    <col min="4" max="4" width="34" style="2" customWidth="1"/>
+    <col min="5" max="5" width="30" style="3" customWidth="1"/>
+    <col min="6" max="6" width="10.625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="18" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="12.75" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="24.95" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="14"/>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="15"/>
+      <c r="G1" s="14"/>
+    </row>
+    <row r="2" spans="1:7" ht="24.95" customHeight="1">
+      <c r="A2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="1:7" ht="24.95" customHeight="1">
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="14"/>
+      <c r="D3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="17"/>
+      <c r="G3" s="18"/>
+    </row>
+    <row r="4" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="14"/>
+    </row>
+    <row r="5" spans="1:7" ht="24.95" customHeight="1">
+      <c r="A5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="14"/>
+    </row>
+    <row r="6" spans="1:7" ht="50.00" customHeight="1">
+      <c r="A6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="14"/>
+    </row>
+    <row r="7" spans="1:7" ht="36" customHeight="1">
+      <c r="A7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A8" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A9" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A10" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A11" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A12" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="50.00" customHeight="1">
+      <c r="A13" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="64.00" customHeight="1">
+      <c r="A14" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A15" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>313</v>
+      </c>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="64.00" customHeight="1">
+      <c r="A16" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="E16" s="11"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10" t="s">
+        <v>319</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B6:G6"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" horizontalDpi="1200" verticalDpi="1200"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultColWidth="12.75" defaultRowHeight="12"/>
+  <cols>
+    <col min="1" max="1" width="9.625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="30" style="3" customWidth="1"/>
+    <col min="3" max="3" width="26" style="3" customWidth="1"/>
+    <col min="4" max="4" width="34" style="2" customWidth="1"/>
+    <col min="5" max="5" width="30" style="3" customWidth="1"/>
+    <col min="6" max="6" width="10.625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="18" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="12.75" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="24.95" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="14"/>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="15"/>
+      <c r="G1" s="14"/>
+    </row>
+    <row r="2" spans="1:7" ht="24.95" customHeight="1">
+      <c r="A2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>320</v>
+      </c>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="1:7" ht="24.95" customHeight="1">
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="14"/>
+      <c r="D3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="17"/>
+      <c r="G3" s="18"/>
+    </row>
+    <row r="4" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="14"/>
+    </row>
+    <row r="5" spans="1:7" ht="24.95" customHeight="1">
+      <c r="A5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>322</v>
+      </c>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="14"/>
+    </row>
+    <row r="6" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="14"/>
+    </row>
+    <row r="7" spans="1:7" ht="36" customHeight="1">
+      <c r="A7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="106.00" customHeight="1">
+      <c r="A8" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>328</v>
+      </c>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A9" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>334</v>
+      </c>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A10" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>338</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="64.00" customHeight="1">
+      <c r="A11" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A12" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>349</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A13" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A14" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A15" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>361</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>362</v>
+      </c>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="78.00" customHeight="1">
+      <c r="A16" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="E16" s="11"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10" t="s">
+        <v>368</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B6:G6"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" horizontalDpi="1200" verticalDpi="1200"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr defaultColWidth="12.75" defaultRowHeight="12"/>
+  <cols>
+    <col min="1" max="1" width="9.625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="30" style="3" customWidth="1"/>
+    <col min="3" max="3" width="26" style="3" customWidth="1"/>
+    <col min="4" max="4" width="34" style="2" customWidth="1"/>
+    <col min="5" max="5" width="30" style="3" customWidth="1"/>
+    <col min="6" max="6" width="10.625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="18" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="12.75" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="24.95" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="14"/>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="15"/>
+      <c r="G1" s="14"/>
+    </row>
+    <row r="2" spans="1:7" ht="24.95" customHeight="1">
+      <c r="A2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>369</v>
+      </c>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="1:7" ht="24.95" customHeight="1">
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="14"/>
+      <c r="D3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="17"/>
+      <c r="G3" s="18"/>
+    </row>
+    <row r="4" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="14"/>
+    </row>
+    <row r="5" spans="1:7" ht="24.95" customHeight="1">
+      <c r="A5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="14"/>
+    </row>
+    <row r="6" spans="1:7" ht="50.00" customHeight="1">
+      <c r="A6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>372</v>
+      </c>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="14"/>
+    </row>
+    <row r="7" spans="1:7" ht="36" customHeight="1">
+      <c r="A7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="106.00" customHeight="1">
+      <c r="A8" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A9" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>381</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>382</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A10" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>385</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>387</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>388</v>
+      </c>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A11" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>392</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A12" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A13" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>405</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>406</v>
+      </c>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="50.00" customHeight="1">
+      <c r="A14" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>411</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A15" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>417</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>418</v>
+      </c>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A16" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>420</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>421</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="50.00" customHeight="1">
+      <c r="A17" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>425</v>
+      </c>
+      <c r="E17" s="11"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="64.00" customHeight="1">
+      <c r="A18" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>428</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>429</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="E18" s="11"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10" t="s">
+        <v>431</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B6:G6"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" horizontalDpi="1200" verticalDpi="1200"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr defaultColWidth="12.75" defaultRowHeight="12"/>
+  <cols>
+    <col min="1" max="1" width="9.625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="30" style="3" customWidth="1"/>
+    <col min="3" max="3" width="26" style="3" customWidth="1"/>
+    <col min="4" max="4" width="34" style="2" customWidth="1"/>
+    <col min="5" max="5" width="30" style="3" customWidth="1"/>
+    <col min="6" max="6" width="10.625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="18" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="12.75" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="24.95" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="14"/>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="15"/>
+      <c r="G1" s="14"/>
+    </row>
+    <row r="2" spans="1:7" ht="24.95" customHeight="1">
+      <c r="A2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>432</v>
+      </c>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="1:7" ht="24.95" customHeight="1">
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="14"/>
+      <c r="D3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="17"/>
+      <c r="G3" s="18"/>
+    </row>
+    <row r="4" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>433</v>
+      </c>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="14"/>
+    </row>
+    <row r="5" spans="1:7" ht="24.95" customHeight="1">
+      <c r="A5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>434</v>
+      </c>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="14"/>
+    </row>
+    <row r="6" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="14"/>
+    </row>
+    <row r="7" spans="1:7" ht="36" customHeight="1">
+      <c r="A7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="92.00" customHeight="1">
+      <c r="A8" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>437</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>439</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>440</v>
+      </c>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="64.00" customHeight="1">
+      <c r="A9" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>443</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>444</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>445</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>446</v>
+      </c>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A10" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>449</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>450</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>451</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>452</v>
+      </c>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A11" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>456</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>457</v>
+      </c>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="50.00" customHeight="1">
+      <c r="A12" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>461</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>462</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>463</v>
+      </c>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A13" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A14" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>471</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>473</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>457</v>
+      </c>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A15" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>475</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>476</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>457</v>
+      </c>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A16" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>479</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>481</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>482</v>
+      </c>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A17" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>484</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>485</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>486</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="50.00" customHeight="1">
+      <c r="A18" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>489</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>490</v>
+      </c>
+      <c r="E18" s="11"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10" t="s">
+        <v>426</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B6:G6"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" horizontalDpi="1200" verticalDpi="1200"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr defaultColWidth="12.75" defaultRowHeight="12"/>
+  <cols>
+    <col min="1" max="1" width="9.625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="30" style="3" customWidth="1"/>
+    <col min="3" max="3" width="26" style="3" customWidth="1"/>
+    <col min="4" max="4" width="34" style="2" customWidth="1"/>
+    <col min="5" max="5" width="30" style="3" customWidth="1"/>
+    <col min="6" max="6" width="10.625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="18" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="12.75" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="24.95" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="14"/>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="15"/>
+      <c r="G1" s="14"/>
+    </row>
+    <row r="2" spans="1:7" ht="24.95" customHeight="1">
+      <c r="A2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>491</v>
+      </c>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="1:7" ht="24.95" customHeight="1">
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="14"/>
+      <c r="D3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="17"/>
+      <c r="G3" s="18"/>
+    </row>
+    <row r="4" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>492</v>
+      </c>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="14"/>
+    </row>
+    <row r="5" spans="1:7" ht="24.95" customHeight="1">
+      <c r="A5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>493</v>
+      </c>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="14"/>
+    </row>
+    <row r="6" spans="1:7" ht="50.00" customHeight="1">
+      <c r="A6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>494</v>
+      </c>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="14"/>
+    </row>
+    <row r="7" spans="1:7" ht="36" customHeight="1">
+      <c r="A7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="50.00" customHeight="1">
+      <c r="A8" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>496</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>497</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>498</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>499</v>
+      </c>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A9" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>502</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>503</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>504</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>499</v>
+      </c>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A10" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>507</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>508</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>509</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>499</v>
+      </c>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A11" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>512</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>513</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A12" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>515</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>516</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>517</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>518</v>
+      </c>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="50.00" customHeight="1">
+      <c r="A13" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>521</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>522</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>523</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>524</v>
+      </c>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="64.00" customHeight="1">
+      <c r="A14" s="9" t="s">
+        <v>526</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>527</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>528</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>529</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>530</v>
+      </c>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="106.00" customHeight="1">
+      <c r="A15" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>533</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>534</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>535</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>536</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>537</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="78.00" customHeight="1">
+      <c r="A16" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>540</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>542</v>
+      </c>
+      <c r="E16" s="11"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="50.00" customHeight="1">
+      <c r="A17" s="9" t="s">
+        <v>544</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>545</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>546</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>548</v>
+      </c>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10" t="s">
+        <v>549</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B6:G6"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" horizontalDpi="1200" verticalDpi="1200"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr defaultColWidth="12.75" defaultRowHeight="12"/>
+  <cols>
+    <col min="1" max="1" width="9.625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="30" style="3" customWidth="1"/>
+    <col min="3" max="3" width="26" style="3" customWidth="1"/>
+    <col min="4" max="4" width="34" style="2" customWidth="1"/>
+    <col min="5" max="5" width="30" style="3" customWidth="1"/>
+    <col min="6" max="6" width="10.625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="18" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="12.75" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="24.95" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="14"/>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="15"/>
+      <c r="G1" s="14"/>
+    </row>
+    <row r="2" spans="1:7" ht="24.95" customHeight="1">
+      <c r="A2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>550</v>
+      </c>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="1:7" ht="24.95" customHeight="1">
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="14"/>
+      <c r="D3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="17"/>
+      <c r="G3" s="18"/>
+    </row>
+    <row r="4" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>551</v>
+      </c>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="14"/>
+    </row>
+    <row r="5" spans="1:7" ht="24.95" customHeight="1">
+      <c r="A5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>552</v>
+      </c>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="14"/>
+    </row>
+    <row r="6" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>553</v>
+      </c>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="14"/>
+    </row>
+    <row r="7" spans="1:7" ht="36" customHeight="1">
+      <c r="A7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="50.00" customHeight="1">
+      <c r="A8" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>555</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>556</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>557</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="50.00" customHeight="1">
+      <c r="A9" s="9" t="s">
+        <v>560</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>562</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>563</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>564</v>
+      </c>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A10" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>568</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>569</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>570</v>
+      </c>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A11" s="9" t="s">
+        <v>571</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>574</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>575</v>
+      </c>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A12" s="9" t="s">
+        <v>577</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>578</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>579</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>580</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>581</v>
+      </c>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A13" s="9" t="s">
+        <v>583</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>584</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>585</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A14" s="9" t="s">
+        <v>587</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>588</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>589</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>590</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>591</v>
+      </c>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="50.00" customHeight="1">
+      <c r="A15" s="9" t="s">
+        <v>593</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>595</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>596</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>362</v>
+      </c>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="36.00" customHeight="1">
+      <c r="A16" s="9" t="s">
+        <v>598</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>599</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>600</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>601</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>602</v>
+      </c>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="50.00" customHeight="1">
+      <c r="A17" s="9" t="s">
+        <v>604</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>605</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>606</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>607</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>608</v>
+      </c>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="50.00" customHeight="1">
+      <c r="A18" s="9" t="s">
+        <v>610</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>611</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>612</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>613</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>614</v>
+      </c>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="64.00" customHeight="1">
+      <c r="A19" s="9" t="s">
+        <v>615</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>616</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>617</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>618</v>
+      </c>
+      <c r="E19" s="11"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10" t="s">
+        <v>619</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B6:G6"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" horizontalDpi="1200" verticalDpi="1200"/>
 </worksheet>
 </file>